--- a/artfynd/A 17976-2025 artfynd.xlsx
+++ b/artfynd/A 17976-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2224,6 +2224,753 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124886260</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stor-Tunberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>622263</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6953220</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Pernilla Hansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Pernilla Hansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124886080</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>622202</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6953261</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Pernilla Hansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Pernilla Hansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124886571</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>622152</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6953168</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Pernilla Hansson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Pernilla Hansson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124886476</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stor-Tunberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>622190</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6953134</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Pernilla Hansson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Pernilla Hansson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124886535</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>622220</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6953138</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Pernilla Hansson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Pernilla Hansson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124888084</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>622163</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6953228</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Pernilla Hansson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Pernilla Hansson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124886164</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stor-Tunberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>622254</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6953267</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Pernilla Hansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Pernilla Hansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17976-2025 artfynd.xlsx
+++ b/artfynd/A 17976-2025 artfynd.xlsx
@@ -2227,10 +2227,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124886260</v>
+        <v>124886535</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2239,41 +2239,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Mpd</t>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622263</v>
+        <v>622220</v>
       </c>
       <c r="R14" t="n">
-        <v>6953220</v>
+        <v>6953138</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2333,7 +2334,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124886080</v>
+        <v>124886476</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2373,14 +2374,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+          <t>Stor-Tunberget, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622202</v>
+        <v>622190</v>
       </c>
       <c r="R15" t="n">
-        <v>6953261</v>
+        <v>6953134</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2440,7 +2441,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124886571</v>
+        <v>124888084</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2484,10 +2485,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622152</v>
+        <v>622163</v>
       </c>
       <c r="R16" t="n">
-        <v>6953168</v>
+        <v>6953228</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2547,7 +2548,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124886476</v>
+        <v>124886571</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2587,14 +2588,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Mpd</t>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622190</v>
+        <v>622152</v>
       </c>
       <c r="R17" t="n">
-        <v>6953134</v>
+        <v>6953168</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2654,10 +2655,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124886535</v>
+        <v>124886164</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2666,42 +2667,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+          <t>Stor-Tunberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622220</v>
+        <v>622254</v>
       </c>
       <c r="R18" t="n">
-        <v>6953138</v>
+        <v>6953267</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2761,7 +2761,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124888084</v>
+        <v>124886080</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2805,10 +2805,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622163</v>
+        <v>622202</v>
       </c>
       <c r="R19" t="n">
-        <v>6953228</v>
+        <v>6953261</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2868,10 +2868,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124886164</v>
+        <v>124886260</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2884,21 +2884,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>622254</v>
+        <v>622263</v>
       </c>
       <c r="R20" t="n">
-        <v>6953267</v>
+        <v>6953220</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 17976-2025 artfynd.xlsx
+++ b/artfynd/A 17976-2025 artfynd.xlsx
@@ -2227,7 +2227,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124886535</v>
+        <v>124886571</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622220</v>
+        <v>622152</v>
       </c>
       <c r="R14" t="n">
-        <v>6953138</v>
+        <v>6953168</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124886476</v>
+        <v>124886535</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2374,14 +2374,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Mpd</t>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622190</v>
+        <v>622220</v>
       </c>
       <c r="R15" t="n">
-        <v>6953134</v>
+        <v>6953138</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2441,7 +2441,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124888084</v>
+        <v>124886080</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622163</v>
+        <v>622202</v>
       </c>
       <c r="R16" t="n">
-        <v>6953228</v>
+        <v>6953261</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2548,7 +2548,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124886571</v>
+        <v>124888084</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622152</v>
+        <v>622163</v>
       </c>
       <c r="R17" t="n">
-        <v>6953168</v>
+        <v>6953228</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2655,10 +2655,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124886164</v>
+        <v>124886260</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2671,21 +2671,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2698,10 +2698,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622254</v>
+        <v>622263</v>
       </c>
       <c r="R18" t="n">
-        <v>6953267</v>
+        <v>6953220</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124886080</v>
+        <v>124886164</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2773,42 +2773,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+          <t>Stor-Tunberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622202</v>
+        <v>622254</v>
       </c>
       <c r="R19" t="n">
-        <v>6953261</v>
+        <v>6953267</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2868,10 +2867,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124886260</v>
+        <v>124886476</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2880,30 +2879,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>622263</v>
+        <v>622190</v>
       </c>
       <c r="R20" t="n">
-        <v>6953220</v>
+        <v>6953134</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 17976-2025 artfynd.xlsx
+++ b/artfynd/A 17976-2025 artfynd.xlsx
@@ -2227,7 +2227,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124886571</v>
+        <v>124886080</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622152</v>
+        <v>622202</v>
       </c>
       <c r="R14" t="n">
-        <v>6953168</v>
+        <v>6953261</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124886535</v>
+        <v>124886476</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2374,14 +2374,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+          <t>Stor-Tunberget, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622220</v>
+        <v>622190</v>
       </c>
       <c r="R15" t="n">
-        <v>6953138</v>
+        <v>6953134</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2441,7 +2441,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124886080</v>
+        <v>124886535</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622202</v>
+        <v>622220</v>
       </c>
       <c r="R16" t="n">
-        <v>6953261</v>
+        <v>6953138</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124886164</v>
+        <v>124886571</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2773,41 +2773,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Mpd</t>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622254</v>
+        <v>622152</v>
       </c>
       <c r="R19" t="n">
-        <v>6953267</v>
+        <v>6953168</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2867,10 +2868,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124886476</v>
+        <v>124886164</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2879,31 +2880,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>622190</v>
+        <v>622254</v>
       </c>
       <c r="R20" t="n">
-        <v>6953134</v>
+        <v>6953267</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 17976-2025 artfynd.xlsx
+++ b/artfynd/A 17976-2025 artfynd.xlsx
@@ -2548,10 +2548,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124888084</v>
+        <v>124886260</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2560,42 +2560,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+          <t>Stor-Tunberget, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622163</v>
+        <v>622263</v>
       </c>
       <c r="R17" t="n">
-        <v>6953228</v>
+        <v>6953220</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2655,10 +2654,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124886260</v>
+        <v>124888084</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2667,41 +2666,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Mpd</t>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622263</v>
+        <v>622163</v>
       </c>
       <c r="R18" t="n">
-        <v>6953220</v>
+        <v>6953228</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>

--- a/artfynd/A 17976-2025 artfynd.xlsx
+++ b/artfynd/A 17976-2025 artfynd.xlsx
@@ -2227,10 +2227,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124886080</v>
+        <v>124886164</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2239,42 +2239,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+          <t>Stor-Tunberget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622202</v>
+        <v>622254</v>
       </c>
       <c r="R14" t="n">
-        <v>6953261</v>
+        <v>6953267</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2441,7 +2440,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124886535</v>
+        <v>124886080</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2485,10 +2484,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622220</v>
+        <v>622202</v>
       </c>
       <c r="R16" t="n">
-        <v>6953138</v>
+        <v>6953261</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2548,10 +2547,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124886260</v>
+        <v>124888084</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2560,41 +2559,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Mpd</t>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622263</v>
+        <v>622163</v>
       </c>
       <c r="R17" t="n">
-        <v>6953220</v>
+        <v>6953228</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2654,7 +2654,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124888084</v>
+        <v>124886571</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2698,10 +2698,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622163</v>
+        <v>622152</v>
       </c>
       <c r="R18" t="n">
-        <v>6953228</v>
+        <v>6953168</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124886571</v>
+        <v>124886260</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2773,42 +2773,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+          <t>Stor-Tunberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622152</v>
+        <v>622263</v>
       </c>
       <c r="R19" t="n">
-        <v>6953168</v>
+        <v>6953220</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2868,10 +2867,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124886164</v>
+        <v>124886535</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2880,41 +2879,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Mpd</t>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>622254</v>
+        <v>622220</v>
       </c>
       <c r="R20" t="n">
-        <v>6953267</v>
+        <v>6953138</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 17976-2025 artfynd.xlsx
+++ b/artfynd/A 17976-2025 artfynd.xlsx
@@ -2227,10 +2227,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124886164</v>
+        <v>124886476</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2239,30 +2239,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2270,10 +2271,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622254</v>
+        <v>622190</v>
       </c>
       <c r="R14" t="n">
-        <v>6953267</v>
+        <v>6953134</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2333,10 +2334,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124886476</v>
+        <v>124886164</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2345,31 +2346,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622190</v>
+        <v>622254</v>
       </c>
       <c r="R15" t="n">
-        <v>6953134</v>
+        <v>6953267</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2440,10 +2440,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124886080</v>
+        <v>124886260</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2452,42 +2452,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+          <t>Stor-Tunberget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622202</v>
+        <v>622263</v>
       </c>
       <c r="R16" t="n">
-        <v>6953261</v>
+        <v>6953220</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2547,7 +2546,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124888084</v>
+        <v>124886571</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2591,10 +2590,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622163</v>
+        <v>622152</v>
       </c>
       <c r="R17" t="n">
-        <v>6953228</v>
+        <v>6953168</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2654,7 +2653,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124886571</v>
+        <v>124888084</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2698,10 +2697,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622152</v>
+        <v>622163</v>
       </c>
       <c r="R18" t="n">
-        <v>6953168</v>
+        <v>6953228</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2761,10 +2760,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124886260</v>
+        <v>124886080</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2773,41 +2772,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Mpd</t>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622263</v>
+        <v>622202</v>
       </c>
       <c r="R19" t="n">
-        <v>6953220</v>
+        <v>6953261</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>

--- a/artfynd/A 17976-2025 artfynd.xlsx
+++ b/artfynd/A 17976-2025 artfynd.xlsx
@@ -2227,10 +2227,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124886476</v>
+        <v>124886260</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2239,31 +2239,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2271,10 +2270,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622190</v>
+        <v>622263</v>
       </c>
       <c r="R14" t="n">
-        <v>6953134</v>
+        <v>6953220</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2334,10 +2333,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124886164</v>
+        <v>124886476</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2346,30 +2345,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622254</v>
+        <v>622190</v>
       </c>
       <c r="R15" t="n">
-        <v>6953267</v>
+        <v>6953134</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2440,10 +2440,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124886260</v>
+        <v>124886080</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2452,41 +2452,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Mpd</t>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622263</v>
+        <v>622202</v>
       </c>
       <c r="R16" t="n">
-        <v>6953220</v>
+        <v>6953261</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2653,10 +2654,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124888084</v>
+        <v>124886164</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2665,42 +2666,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+          <t>Stor-Tunberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622163</v>
+        <v>622254</v>
       </c>
       <c r="R18" t="n">
-        <v>6953228</v>
+        <v>6953267</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2760,7 +2760,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124886080</v>
+        <v>124886535</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622202</v>
+        <v>622220</v>
       </c>
       <c r="R19" t="n">
-        <v>6953261</v>
+        <v>6953138</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2867,7 +2867,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124886535</v>
+        <v>124888084</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>622220</v>
+        <v>622163</v>
       </c>
       <c r="R20" t="n">
-        <v>6953138</v>
+        <v>6953228</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 17976-2025 artfynd.xlsx
+++ b/artfynd/A 17976-2025 artfynd.xlsx
@@ -2227,10 +2227,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124886260</v>
+        <v>124886080</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2239,41 +2239,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Mpd</t>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622263</v>
+        <v>622202</v>
       </c>
       <c r="R14" t="n">
-        <v>6953220</v>
+        <v>6953261</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2440,7 +2441,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124886080</v>
+        <v>124886571</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2484,10 +2485,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622202</v>
+        <v>622152</v>
       </c>
       <c r="R16" t="n">
-        <v>6953261</v>
+        <v>6953168</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2547,7 +2548,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124886571</v>
+        <v>124886535</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2591,10 +2592,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622152</v>
+        <v>622220</v>
       </c>
       <c r="R17" t="n">
-        <v>6953168</v>
+        <v>6953138</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2654,10 +2655,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124886164</v>
+        <v>124888084</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2666,41 +2667,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Mpd</t>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622254</v>
+        <v>622163</v>
       </c>
       <c r="R18" t="n">
-        <v>6953267</v>
+        <v>6953228</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2760,10 +2762,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124886535</v>
+        <v>124886260</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2772,42 +2774,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+          <t>Stor-Tunberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622220</v>
+        <v>622263</v>
       </c>
       <c r="R19" t="n">
-        <v>6953138</v>
+        <v>6953220</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2867,10 +2868,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124888084</v>
+        <v>124886164</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2879,42 +2880,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+          <t>Stor-Tunberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>622163</v>
+        <v>622254</v>
       </c>
       <c r="R20" t="n">
-        <v>6953228</v>
+        <v>6953267</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 17976-2025 artfynd.xlsx
+++ b/artfynd/A 17976-2025 artfynd.xlsx
@@ -2227,7 +2227,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124886080</v>
+        <v>124886476</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2267,14 +2267,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+          <t>Stor-Tunberget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622202</v>
+        <v>622190</v>
       </c>
       <c r="R14" t="n">
-        <v>6953261</v>
+        <v>6953134</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124886476</v>
+        <v>124886080</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2374,14 +2374,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Mpd</t>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622190</v>
+        <v>622202</v>
       </c>
       <c r="R15" t="n">
-        <v>6953134</v>
+        <v>6953261</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2548,10 +2548,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124886535</v>
+        <v>124886260</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2560,42 +2560,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+          <t>Stor-Tunberget, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622220</v>
+        <v>622263</v>
       </c>
       <c r="R17" t="n">
-        <v>6953138</v>
+        <v>6953220</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2762,10 +2761,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124886260</v>
+        <v>124886164</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2778,21 +2777,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2805,10 +2804,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622263</v>
+        <v>622254</v>
       </c>
       <c r="R19" t="n">
-        <v>6953220</v>
+        <v>6953267</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2868,10 +2867,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124886164</v>
+        <v>124886535</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2880,41 +2879,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Mpd</t>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>622254</v>
+        <v>622220</v>
       </c>
       <c r="R20" t="n">
-        <v>6953267</v>
+        <v>6953138</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 17976-2025 artfynd.xlsx
+++ b/artfynd/A 17976-2025 artfynd.xlsx
@@ -2227,7 +2227,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124886476</v>
+        <v>124886571</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2267,14 +2267,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Mpd</t>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622190</v>
+        <v>622152</v>
       </c>
       <c r="R14" t="n">
-        <v>6953134</v>
+        <v>6953168</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124886080</v>
+        <v>124888084</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622202</v>
+        <v>622163</v>
       </c>
       <c r="R15" t="n">
-        <v>6953261</v>
+        <v>6953228</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2441,7 +2441,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124886571</v>
+        <v>124886535</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622152</v>
+        <v>622220</v>
       </c>
       <c r="R16" t="n">
-        <v>6953168</v>
+        <v>6953138</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2548,10 +2548,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124886260</v>
+        <v>124886080</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2560,41 +2560,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Mpd</t>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622263</v>
+        <v>622202</v>
       </c>
       <c r="R17" t="n">
-        <v>6953220</v>
+        <v>6953261</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2654,7 +2655,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124888084</v>
+        <v>124886476</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2694,14 +2695,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+          <t>Stor-Tunberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622163</v>
+        <v>622190</v>
       </c>
       <c r="R18" t="n">
-        <v>6953228</v>
+        <v>6953134</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2867,10 +2868,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124886535</v>
+        <v>124886260</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2879,42 +2880,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+          <t>Stor-Tunberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>622220</v>
+        <v>622263</v>
       </c>
       <c r="R20" t="n">
-        <v>6953138</v>
+        <v>6953220</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 17976-2025 artfynd.xlsx
+++ b/artfynd/A 17976-2025 artfynd.xlsx
@@ -2227,7 +2227,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124886571</v>
+        <v>124886080</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622152</v>
+        <v>622202</v>
       </c>
       <c r="R14" t="n">
-        <v>6953168</v>
+        <v>6953261</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2334,10 +2334,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124888084</v>
+        <v>124886164</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2346,42 +2346,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+          <t>Stor-Tunberget, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622163</v>
+        <v>622254</v>
       </c>
       <c r="R15" t="n">
-        <v>6953228</v>
+        <v>6953267</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2441,7 +2440,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124886535</v>
+        <v>124888084</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2485,10 +2484,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622220</v>
+        <v>622163</v>
       </c>
       <c r="R16" t="n">
-        <v>6953138</v>
+        <v>6953228</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2548,7 +2547,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124886080</v>
+        <v>124886476</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2588,14 +2587,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+          <t>Stor-Tunberget, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622202</v>
+        <v>622190</v>
       </c>
       <c r="R17" t="n">
-        <v>6953261</v>
+        <v>6953134</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2655,7 +2654,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124886476</v>
+        <v>124886571</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2695,14 +2694,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Mpd</t>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622190</v>
+        <v>622152</v>
       </c>
       <c r="R18" t="n">
-        <v>6953134</v>
+        <v>6953168</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2762,10 +2761,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124886164</v>
+        <v>124886535</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2774,41 +2773,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Mpd</t>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622254</v>
+        <v>622220</v>
       </c>
       <c r="R19" t="n">
-        <v>6953267</v>
+        <v>6953138</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>

--- a/artfynd/A 17976-2025 artfynd.xlsx
+++ b/artfynd/A 17976-2025 artfynd.xlsx
@@ -2227,10 +2227,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124886080</v>
+        <v>124886164</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>91166</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2239,42 +2239,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+          <t>Stor-Tunberget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622202</v>
+        <v>622254</v>
       </c>
       <c r="R14" t="n">
-        <v>6953261</v>
+        <v>6953267</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2334,10 +2333,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124886164</v>
+        <v>124886476</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2346,30 +2345,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622254</v>
+        <v>622190</v>
       </c>
       <c r="R15" t="n">
-        <v>6953267</v>
+        <v>6953134</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2440,10 +2440,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124888084</v>
+        <v>124886260</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>80028</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2452,42 +2452,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+          <t>Stor-Tunberget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622163</v>
+        <v>622263</v>
       </c>
       <c r="R16" t="n">
-        <v>6953228</v>
+        <v>6953220</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2547,10 +2546,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124886476</v>
+        <v>124886535</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2587,14 +2586,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Mpd</t>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622190</v>
+        <v>622220</v>
       </c>
       <c r="R17" t="n">
-        <v>6953134</v>
+        <v>6953138</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2654,10 +2653,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124886571</v>
+        <v>124886080</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2698,10 +2697,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622152</v>
+        <v>622202</v>
       </c>
       <c r="R18" t="n">
-        <v>6953168</v>
+        <v>6953261</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2761,10 +2760,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124886535</v>
+        <v>124888084</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2805,10 +2804,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622220</v>
+        <v>622163</v>
       </c>
       <c r="R19" t="n">
-        <v>6953138</v>
+        <v>6953228</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2868,10 +2867,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124886260</v>
+        <v>124886571</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>98269</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2880,41 +2879,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Mpd</t>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>622263</v>
+        <v>622152</v>
       </c>
       <c r="R20" t="n">
-        <v>6953220</v>
+        <v>6953168</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 17976-2025 artfynd.xlsx
+++ b/artfynd/A 17976-2025 artfynd.xlsx
@@ -2227,10 +2227,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124886164</v>
+        <v>124886080</v>
       </c>
       <c r="B14" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2239,41 +2239,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Mpd</t>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622254</v>
+        <v>622202</v>
       </c>
       <c r="R14" t="n">
-        <v>6953267</v>
+        <v>6953261</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2333,10 +2334,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124886476</v>
+        <v>124886260</v>
       </c>
       <c r="B15" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2345,31 +2346,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622190</v>
+        <v>622263</v>
       </c>
       <c r="R15" t="n">
-        <v>6953134</v>
+        <v>6953220</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2440,10 +2440,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124886260</v>
+        <v>124886535</v>
       </c>
       <c r="B16" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2452,41 +2452,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Mpd</t>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622263</v>
+        <v>622220</v>
       </c>
       <c r="R16" t="n">
-        <v>6953220</v>
+        <v>6953138</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2546,7 +2547,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124886535</v>
+        <v>124886571</v>
       </c>
       <c r="B17" t="n">
         <v>98269</v>
@@ -2590,10 +2591,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622220</v>
+        <v>622152</v>
       </c>
       <c r="R17" t="n">
-        <v>6953138</v>
+        <v>6953168</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2653,10 +2654,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124886080</v>
+        <v>124886164</v>
       </c>
       <c r="B18" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2665,42 +2666,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+          <t>Stor-Tunberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622202</v>
+        <v>622254</v>
       </c>
       <c r="R18" t="n">
-        <v>6953261</v>
+        <v>6953267</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2760,7 +2760,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124888084</v>
+        <v>124886476</v>
       </c>
       <c r="B19" t="n">
         <v>98269</v>
@@ -2800,14 +2800,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+          <t>Stor-Tunberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622163</v>
+        <v>622190</v>
       </c>
       <c r="R19" t="n">
-        <v>6953228</v>
+        <v>6953134</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2867,7 +2867,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124886571</v>
+        <v>124888084</v>
       </c>
       <c r="B20" t="n">
         <v>98269</v>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>622152</v>
+        <v>622163</v>
       </c>
       <c r="R20" t="n">
-        <v>6953168</v>
+        <v>6953228</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 17976-2025 artfynd.xlsx
+++ b/artfynd/A 17976-2025 artfynd.xlsx
@@ -2232,11 +2232,6 @@
       <c r="B14" t="n">
         <v>98269</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>VU</t>
@@ -2334,53 +2329,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124886260</v>
+        <v>124886571</v>
       </c>
       <c r="B15" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Mpd</t>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622263</v>
+        <v>622152</v>
       </c>
       <c r="R15" t="n">
-        <v>6953220</v>
+        <v>6953168</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2440,54 +2431,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124886535</v>
+        <v>124886164</v>
       </c>
       <c r="B16" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+          <t>Stor-Tunberget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622220</v>
+        <v>622254</v>
       </c>
       <c r="R16" t="n">
-        <v>6953138</v>
+        <v>6953267</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2547,15 +2532,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124886571</v>
+        <v>124886476</v>
       </c>
       <c r="B17" t="n">
         <v>98269</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2587,14 +2567,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
+          <t>Stor-Tunberget, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622152</v>
+        <v>622190</v>
       </c>
       <c r="R17" t="n">
-        <v>6953168</v>
+        <v>6953134</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2654,53 +2634,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124886164</v>
+        <v>124886535</v>
       </c>
       <c r="B18" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor-Tunberget, Mpd</t>
+          <t>Stor-Tunberget, Stor-Tunberget, Ljustorp, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622254</v>
+        <v>622220</v>
       </c>
       <c r="R18" t="n">
-        <v>6953267</v>
+        <v>6953138</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2760,43 +2736,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124886476</v>
+        <v>124886260</v>
       </c>
       <c r="B19" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2804,10 +2774,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622190</v>
+        <v>622263</v>
       </c>
       <c r="R19" t="n">
-        <v>6953134</v>
+        <v>6953220</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2871,11 +2841,6 @@
       </c>
       <c r="B20" t="n">
         <v>98269</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
